--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486732_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486732_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7617</v>
+        <v>9.5</v>
       </c>
       <c r="E2" t="n">
-        <v>8.852499999999999</v>
+        <v>7.8391</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9092</v>
+        <v>1.6609</v>
       </c>
       <c r="G2" t="n">
         <v>3.4524</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>2.372</v>
+        <v>1.1103</v>
       </c>
       <c r="T2" t="n">
-        <v>1.737</v>
+        <v>0.7236</v>
       </c>
       <c r="U2" t="n">
-        <v>0.635</v>
+        <v>0.3867</v>
       </c>
       <c r="V2" t="n">
         <v>6.0958</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7022</v>
+        <v>5.2195</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8686</v>
+        <v>4.1376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8336</v>
+        <v>1.0819</v>
       </c>
       <c r="G3" t="n">
         <v>3.7645</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2207</v>
+        <v>0.2966</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0548</v>
+        <v>0.3238</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2756</v>
+        <v>-0.0272</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3851</v>
+        <v>3.8961</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6839</v>
+        <v>3.2034</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7013</v>
+        <v>0.6926</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0764</v>
+        <v>5.5265</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0621</v>
+        <v>2.642</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0143</v>
+        <v>2.8846</v>
       </c>
       <c r="J4" t="n">
-        <v>1.436</v>
+        <v>4.5414</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2823</v>
+        <v>2.5045</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7182</v>
+        <v>2.0369</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6404</v>
+        <v>0.9851</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3443</v>
+        <v>0.1374</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2961</v>
+        <v>0.8477</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4359</v>
+        <v>-0.2756</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2479</v>
+        <v>0.0135</v>
       </c>
       <c r="U4" t="n">
-        <v>0.188</v>
+        <v>-0.2892</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2856</v>
+        <v>-2.1271</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0796</v>
+        <v>3.6044</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3622</v>
+        <v>1.9528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7175</v>
+        <v>1.6516</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5265</v>
+        <v>2.0764</v>
       </c>
       <c r="H5" t="n">
-        <v>2.642</v>
+        <v>0.0621</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8846</v>
+        <v>2.0143</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5414</v>
+        <v>1.436</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5045</v>
+        <v>-0.2823</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0369</v>
+        <v>1.7182</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9851</v>
+        <v>0.6404</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1374</v>
+        <v>0.3443</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8477</v>
+        <v>0.2961</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0921</v>
+        <v>0.6552</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8277</v>
+        <v>0.5169</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2643</v>
+        <v>0.1383</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1271</v>
+        <v>-0.2856</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1271</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,37 +877,37 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3248</v>
+        <v>2.0593</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5171</v>
+        <v>1.5938</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8076</v>
+        <v>0.4655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2892</v>
+        <v>1.8138</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8207</v>
+        <v>0.7446</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1099</v>
+        <v>1.0692</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4203</v>
+        <v>2.1388</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2341</v>
+        <v>1.3657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8138</v>
+        <v>0.7732</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7095</v>
+        <v>-0.325</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4134</v>
+        <v>-0.6211</v>
       </c>
       <c r="O6" t="n">
         <v>0.2961</v>
@@ -916,34 +916,34 @@
         <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0702</v>
+        <v>-0.4343</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9374</v>
+        <v>-0.1588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1328</v>
+        <v>-0.2755</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,37 +955,37 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9422</v>
+        <v>1.9235</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2284</v>
+        <v>0.1656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7138</v>
+        <v>1.758</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8138</v>
+        <v>0.2892</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7446</v>
+        <v>-0.8207</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0692</v>
+        <v>1.1099</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1388</v>
+        <v>-0.4203</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3657</v>
+        <v>-1.2341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7732</v>
+        <v>0.8138</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.325</v>
+        <v>0.7095</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6211</v>
+        <v>0.4134</v>
       </c>
       <c r="O7" t="n">
         <v>0.2961</v>
@@ -994,28 +994,28 @@
         <v>0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5515</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5243</v>
+        <v>0.5858</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0272</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3574</v>
+        <v>-0.2759</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4546</v>
+        <v>-0.4476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1717</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8965</v>
@@ -1078,13 +1078,13 @@
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1986</v>
+        <v>-0.1172</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5238</v>
+        <v>0.5308</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7224</v>
+        <v>-0.6479</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRÍGUEZ</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8973</v>
+        <v>-1.0989</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8142</v>
+        <v>-2.1846</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08309999999999999</v>
+        <v>1.0856</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0076</v>
+        <v>-2.1784</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2275</v>
+        <v>-2.427</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2351</v>
+        <v>0.2486</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6281</v>
+        <v>-2.6806</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0207</v>
+        <v>-2.3573</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>-0.3232</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.5022</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2068</v>
+        <v>-0.0697</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4137</v>
+        <v>0.5719</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5792</v>
+        <v>2.1239</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0827</v>
+        <v>0.4689</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2207</v>
+        <v>0.6891</v>
       </c>
       <c r="U9" t="n">
-        <v>0.138</v>
+        <v>-0.2203</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>G. CAMPOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0865</v>
+        <v>-1.7387</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8742</v>
+        <v>-1.6556</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7876</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1784</v>
+        <v>-0.0076</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.427</v>
+        <v>0.2275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2486</v>
+        <v>-0.2351</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6806</v>
+        <v>-0.6281</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3573</v>
+        <v>0.0207</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3232</v>
+        <v>-0.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5022</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0697</v>
+        <v>0.2068</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5719</v>
+        <v>0.4137</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1239</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3169</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5187</v>
+        <v>0.0759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0005</v>
+        <v>-0.0621</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5182</v>
+        <v>0.138</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2529</v>
+        <v>-2.2171</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2961</v>
+        <v>-1.1858</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9568</v>
+        <v>-1.0313</v>
       </c>
       <c r="G11" t="n">
         <v>1.2862</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5848</v>
+        <v>0.6206</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3858</v>
+        <v>0.4962</v>
       </c>
       <c r="U11" t="n">
-        <v>0.199</v>
+        <v>0.1245</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9032</v>
+        <v>-3.5185</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3733</v>
+        <v>-2.0631</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5299</v>
+        <v>-1.4554</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8149999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2813</v>
+        <v>0.1035</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1104</v>
+        <v>0.1999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.6983</v>
+        <v>17.3537</v>
       </c>
       <c r="E13" t="n">
-        <v>9.700299999999999</v>
+        <v>11.3556</v>
       </c>
       <c r="F13" t="n">
-        <v>5.997999999999999</v>
+        <v>5.998</v>
       </c>
       <c r="G13" t="n">
         <v>14.3115</v>
@@ -1459,7 +1459,7 @@
         <v>1.6159</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8962</v>
+        <v>2.896199999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.5847</v>
@@ -1468,13 +1468,13 @@
         <v>14.4809</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5173</v>
+        <v>3.1728</v>
       </c>
       <c r="T13" t="n">
-        <v>2.203100000000001</v>
+        <v>3.8587</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6858</v>
+        <v>-0.6859999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0265</v>
@@ -1483,7 +1483,7 @@
         <v>6.381399999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.4079</v>
+        <v>-9.407900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7025</v>
+        <v>4.621</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3908</v>
+        <v>5.5977</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6883</v>
+        <v>-0.9766</v>
       </c>
       <c r="G14" t="n">
         <v>2.0103</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1807</v>
+        <v>-0.2621</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1384</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0423</v>
+        <v>-0.3306</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4101</v>
+        <v>1.3332</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7983</v>
+        <v>1.1435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6119</v>
+        <v>0.1897</v>
       </c>
       <c r="G15" t="n">
         <v>1.6949</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>3.194</v>
+        <v>1.1171</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4267</v>
+        <v>0.772</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7673</v>
+        <v>0.3451</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8995</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2557</v>
+        <v>0.0257</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0261</v>
+        <v>0.233</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2818</v>
+        <v>-0.2073</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3053</v>
@@ -1702,13 +1702,13 @@
         <v>0.3862</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3365</v>
+        <v>-0.0552</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.138</v>
+        <v>0.0688</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1985</v>
+        <v>-0.124</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4413</v>
+        <v>-0.669</v>
       </c>
       <c r="E17" t="n">
-        <v>0.306</v>
+        <v>-0.0552</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7473</v>
+        <v>-0.6138</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2179</v>
+        <v>-0.3381</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5447</v>
+        <v>0.0689</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7626</v>
+        <v>-0.4069</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4731</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2696</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2035</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.691</v>
+        <v>-0.3381</v>
       </c>
       <c r="N17" t="n">
-        <v>0.275</v>
+        <v>0.0689</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9661</v>
+        <v>-0.4069</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4565</v>
+        <v>-0.331</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1579</v>
+        <v>-0.0552</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2986</v>
+        <v>-0.2758</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.669</v>
+        <v>-0.9273</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0552</v>
+        <v>0.0329</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6138</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3381</v>
+        <v>-4.1266</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0689</v>
+        <v>-0.0347</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4069</v>
+        <v>-4.0918</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-2.256</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.3096</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.9464</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3381</v>
+        <v>-1.8706</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0689</v>
+        <v>0.2749</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4069</v>
+        <v>-2.1454</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.331</v>
+        <v>0.0688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0552</v>
+        <v>0.0546</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2758</v>
+        <v>0.0142</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.8681</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>6.0958</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0775</v>
+        <v>-1.5047</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3808</v>
+        <v>-0.6248</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6967</v>
+        <v>-0.8799</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1266</v>
+        <v>-1.2179</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0347</v>
+        <v>1.5447</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.0918</v>
+        <v>-2.7626</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.256</v>
+        <v>1.4731</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3096</v>
+        <v>1.2696</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9464</v>
+        <v>0.2035</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8706</v>
+        <v>-2.691</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2749</v>
+        <v>0.275</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1454</v>
+        <v>-2.9661</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7377</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8616</v>
+        <v>-2.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0814</v>
+        <v>0.393</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3591</v>
+        <v>0.2271</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7223000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8681</v>
+        <v>0.2856</v>
       </c>
       <c r="W19" t="n">
-        <v>6.0958</v>
+        <v>0.5712</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2321</v>
+        <v>-1.7977</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8936</v>
+        <v>-1.5833</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3385</v>
+        <v>-0.2143</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9357</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.331</v>
+        <v>0.1034</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4691</v>
+        <v>-0.1588</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1381</v>
+        <v>0.2622</v>
       </c>
       <c r="V20" t="n">
         <v>0.6138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8104</v>
+        <v>-2.8299</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5391</v>
+        <v>-3.022</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2713</v>
+        <v>0.1921</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1405</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1252</v>
+        <v>-0.1448</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4968</v>
+        <v>0.0204</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.1651</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2443</v>
+        <v>-3.4859</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.119</v>
+        <v>-2.4985</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1253</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8166</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9377</v>
+        <v>-0.1793</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9657</v>
+        <v>-0.3452</v>
       </c>
       <c r="U22" t="n">
-        <v>0.028</v>
+        <v>0.1659</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2863</v>
+        <v>-3.7485</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6579</v>
+        <v>-1.2442</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6285</v>
+        <v>-2.5043</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2311</v>
@@ -2248,13 +2248,13 @@
         <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6345</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6623</v>
+        <v>-0.2486</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0278</v>
+        <v>0.152</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8415</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7943</v>
+        <v>-4.6467</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8737</v>
+        <v>-3.9771</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9206</v>
+        <v>-0.6696</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9049</v>
@@ -2326,13 +2326,13 @@
         <v>0.9654</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2096</v>
+        <v>-0.0621</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3859</v>
+        <v>0.2825</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5956</v>
+        <v>-0.3446</v>
       </c>
       <c r="V24" t="n">
         <v>0.2856</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.6983</v>
+        <v>-13.6298</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.998099999999999</v>
+        <v>-5.998</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.700200000000001</v>
+        <v>-7.6316</v>
       </c>
       <c r="G25" t="n">
         <v>-14.3115</v>
@@ -2377,7 +2377,7 @@
         <v>-16.3784</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.611099999999999</v>
+        <v>-1.6111</v>
       </c>
       <c r="K25" t="n">
         <v>0.004700000000000149</v>
@@ -2395,7 +2395,7 @@
         <v>-14.7627</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.896000000000001</v>
+        <v>-2.896</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.481</v>
@@ -2404,13 +2404,13 @@
         <v>11.5849</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5171</v>
+        <v>0.5511999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6859</v>
+        <v>0.6861000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2032</v>
+        <v>-0.1347</v>
       </c>
       <c r="V25" t="n">
         <v>3.0265</v>
